--- a/ALLY_LOTTE_WH/DATA/0627_棧板資訊_v8.3匯入.xlsx
+++ b/ALLY_LOTTE_WH/DATA/0627_棧板資訊_v8.3匯入.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J445"/>
+  <dimension ref="A1:L445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,16 @@
           <t>ean</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>alloc_batch_id</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>alloc_timestamp</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -507,6 +517,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BATCH_00001</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -547,6 +567,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BATCH_00002</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -587,6 +617,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BATCH_00003</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -627,6 +667,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>BATCH_00004</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -667,6 +717,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>BATCH_00005</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -707,6 +767,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>BATCH_00006</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -747,6 +817,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>BATCH_00007</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -787,6 +867,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>BATCH_00008</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -827,6 +917,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>BATCH_00009</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -867,6 +967,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>BATCH_00010</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -907,6 +1017,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>BATCH_00011</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -947,6 +1067,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>BATCH_00012</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -987,6 +1117,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>BATCH_00013</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1027,6 +1167,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>BATCH_00014</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1067,6 +1217,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>BATCH_00015</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1107,6 +1267,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>BATCH_00016</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1147,6 +1317,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>BATCH_00017</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1187,6 +1367,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>BATCH_00018</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1227,6 +1417,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>BATCH_00019</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1267,6 +1467,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>BATCH_00020</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1307,6 +1517,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>BATCH_00021</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1347,6 +1567,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>BATCH_00022</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1387,6 +1617,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>BATCH_00023</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1427,6 +1667,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>BATCH_00024</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1467,6 +1717,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>BATCH_00025</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1507,6 +1767,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>BATCH_00026</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -1547,6 +1817,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>BATCH_00027</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -1587,6 +1867,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>BATCH_00028</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -1627,6 +1917,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>BATCH_00029</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -1667,6 +1967,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>BATCH_00030</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -1707,6 +2017,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>BATCH_00031</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -1747,6 +2067,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>BATCH_00032</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -1787,6 +2117,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>BATCH_00033</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -1827,6 +2167,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>BATCH_00034</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -1867,6 +2217,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>BATCH_00035</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -1907,6 +2267,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>BATCH_00036</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -1947,6 +2317,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>BATCH_00037</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -1987,6 +2367,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>BATCH_00038</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -2027,6 +2417,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>BATCH_00039</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -2067,6 +2467,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>BATCH_00040</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -2107,6 +2517,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>BATCH_00041</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -2147,6 +2567,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>BATCH_00042</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -2187,6 +2617,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>BATCH_00043</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -2227,6 +2667,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>BATCH_00044</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -2267,6 +2717,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>BATCH_00045</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -2307,6 +2767,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>BATCH_00046</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -2347,6 +2817,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>BATCH_00047</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -2387,6 +2867,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>BATCH_00048</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -2427,6 +2917,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>BATCH_00049</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -2467,6 +2967,16 @@
           <t>58852008304867</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>BATCH_00050</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -2507,6 +3017,16 @@
           <t>58852008304898</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>BATCH_00051</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -2547,6 +3067,16 @@
           <t>58852008304898</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>BATCH_00052</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -2587,6 +3117,16 @@
           <t>58852008304898</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>BATCH_00053</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -2627,6 +3167,16 @@
           <t>58852008304898</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>BATCH_00054</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -2667,6 +3217,16 @@
           <t>58852008304898</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>BATCH_00055</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -2707,6 +3267,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>BATCH_00056</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -2747,6 +3317,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>BATCH_00057</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -2787,6 +3367,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>BATCH_00058</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -2827,6 +3417,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>BATCH_00059</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -2867,6 +3467,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>BATCH_00060</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -2907,6 +3517,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>BATCH_00061</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -2947,6 +3567,16 @@
           <t>58852008304911</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>BATCH_00062</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -2987,6 +3617,16 @@
           <t>58852008305390</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>BATCH_00063</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -3027,6 +3667,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>BATCH_00064</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -3067,6 +3717,16 @@
           <t>58852008304911</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>BATCH_00065</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -3107,6 +3767,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>BATCH_00066</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -3147,6 +3817,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>BATCH_00067</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -3187,6 +3867,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>BATCH_00068</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -3227,6 +3917,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>BATCH_00069</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -3267,6 +3967,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>BATCH_00070</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -3307,6 +4017,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>BATCH_00071</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -3347,6 +4067,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>BATCH_00072</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -3387,6 +4117,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>BATCH_00073</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -3427,6 +4167,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>BATCH_00074</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -3467,6 +4217,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>BATCH_00075</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -3507,6 +4267,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>BATCH_00076</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -3547,6 +4317,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>BATCH_00077</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -3587,6 +4367,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>BATCH_00078</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -3627,6 +4417,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>BATCH_00079</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
@@ -3667,6 +4467,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>BATCH_00080</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
@@ -3707,6 +4517,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>BATCH_00081</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
@@ -3747,6 +4567,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>BATCH_00082</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
@@ -3787,6 +4617,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>BATCH_00083</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
@@ -3827,6 +4667,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>BATCH_00084</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
@@ -3867,6 +4717,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>BATCH_00085</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
@@ -3907,6 +4767,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>BATCH_00086</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
@@ -3947,6 +4817,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>BATCH_00087</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
@@ -3987,6 +4867,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>BATCH_00088</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
@@ -4027,6 +4917,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>BATCH_00089</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
@@ -4067,6 +4967,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>BATCH_00090</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
@@ -4107,6 +5017,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>BATCH_00091</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
@@ -4147,6 +5067,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>BATCH_00092</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
@@ -4187,6 +5117,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>BATCH_00093</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
@@ -4227,6 +5167,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>BATCH_00094</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
@@ -4267,6 +5217,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>BATCH_00095</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
@@ -4307,6 +5267,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>BATCH_00096</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
@@ -4347,6 +5317,16 @@
           <t>18801019930741</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>BATCH_00097</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
@@ -4387,6 +5367,16 @@
           <t>18801019930741</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>BATCH_00098</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
@@ -4427,6 +5417,16 @@
           <t>18801019930741</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>BATCH_00099</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
@@ -4467,6 +5467,16 @@
           <t>18801019930741</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>BATCH_00100</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
@@ -4507,6 +5517,16 @@
           <t>18801019930741</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>BATCH_00101</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
@@ -4547,6 +5567,16 @@
           <t>18801019930741</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>BATCH_00102</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
@@ -4587,6 +5617,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>BATCH_00103</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
@@ -4627,6 +5667,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>BATCH_00104</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
@@ -4667,6 +5717,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>BATCH_00105</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
@@ -4707,6 +5767,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>BATCH_00106</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
@@ -4747,6 +5817,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>BATCH_00107</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
@@ -4787,6 +5867,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>BATCH_00108</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
@@ -4827,6 +5917,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>BATCH_00109</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
@@ -4867,6 +5967,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>BATCH_00110</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
@@ -4907,6 +6017,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>BATCH_00111</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
@@ -4947,6 +6067,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>BATCH_00112</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
@@ -4987,6 +6117,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>BATCH_00113</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
@@ -5027,6 +6167,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>BATCH_00114</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
@@ -5067,6 +6217,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>BATCH_00115</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
@@ -5107,6 +6267,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>BATCH_00116</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
@@ -5147,6 +6317,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>BATCH_00117</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
@@ -5187,6 +6367,16 @@
           <t>14712834455187</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>BATCH_00118</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
@@ -5227,6 +6417,16 @@
           <t>14712834455187</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>BATCH_00119</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
@@ -5267,6 +6467,16 @@
           <t>14712834455187</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>BATCH_00120</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
@@ -5307,6 +6517,16 @@
           <t>14712834455187</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>BATCH_00121</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
@@ -5347,6 +6567,16 @@
           <t>04712834456378</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>BATCH_00122</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
@@ -5387,6 +6617,16 @@
           <t>04712834456378</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>BATCH_00123</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
@@ -5427,6 +6667,16 @@
           <t>04712834456378</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>BATCH_00124</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
@@ -5467,6 +6717,16 @@
           <t>04712834456378</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>BATCH_00125</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
@@ -5507,6 +6767,16 @@
           <t>04712834457153</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>BATCH_00126</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
@@ -5547,6 +6817,16 @@
           <t>0712834457160</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>BATCH_00127</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
@@ -5583,6 +6863,16 @@
           <t>4712834457344</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>PENDING_00001</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
@@ -5623,6 +6913,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>BATCH_00128</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
@@ -5663,6 +6963,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>BATCH_00129</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
@@ -5703,6 +7013,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>BATCH_00130</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
@@ -5743,6 +7063,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>BATCH_00131</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
@@ -5783,6 +7113,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>BATCH_00132</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
@@ -5823,6 +7163,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>BATCH_00133</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
@@ -5863,6 +7213,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>BATCH_00134</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
@@ -5903,6 +7263,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>BATCH_00135</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
@@ -5943,6 +7313,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>BATCH_00136</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
@@ -5983,6 +7363,16 @@
           <t>18801062899613</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>BATCH_00137</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
@@ -6023,6 +7413,16 @@
           <t>18801062899613</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>BATCH_00138</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
@@ -6063,6 +7463,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>BATCH_00139</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
@@ -6103,6 +7513,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>BATCH_00140</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
@@ -6143,6 +7563,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>BATCH_00141</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
@@ -6183,6 +7613,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>BATCH_00142</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
@@ -6223,6 +7663,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>BATCH_00143</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
@@ -6263,6 +7713,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>BATCH_00144</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
@@ -6303,6 +7763,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>BATCH_00145</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
@@ -6343,6 +7813,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>BATCH_00146</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
@@ -6383,6 +7863,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>BATCH_00147</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
@@ -6423,6 +7913,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>BATCH_00148</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
@@ -6463,6 +7963,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>BATCH_00149</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
@@ -6503,6 +8013,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>BATCH_00150</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
@@ -6543,6 +8063,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>BATCH_00151</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
@@ -6583,6 +8113,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>BATCH_00152</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
@@ -6623,6 +8163,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>BATCH_00153</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
@@ -6663,6 +8213,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>BATCH_00154</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
@@ -6703,6 +8263,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>BATCH_00155</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
@@ -6743,6 +8313,16 @@
           <t>58852008511258</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>BATCH_00156</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
@@ -6779,6 +8359,16 @@
           <t>0712834457160</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>PENDING_00002</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
@@ -6815,6 +8405,16 @@
           <t>0712834457160</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>PENDING_00003</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
@@ -6851,6 +8451,16 @@
           <t>0712834457160</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>PENDING_00004</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
@@ -6891,6 +8501,16 @@
           <t>0712834457160</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>BATCH_00157</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
@@ -6931,6 +8551,16 @@
           <t>18801062000781</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>BATCH_00158</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
@@ -6971,6 +8601,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>BATCH_00159</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
@@ -7011,6 +8651,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>BATCH_00160</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
@@ -7051,6 +8701,16 @@
           <t>28801062475135</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>BATCH_00161</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
@@ -7091,6 +8751,16 @@
           <t>8935341300736</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>BATCH_00162</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
@@ -7131,6 +8801,16 @@
           <t>8935341300736</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>BATCH_00163</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
@@ -7171,6 +8851,16 @@
           <t>08935341301337</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>BATCH_00164</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
@@ -7211,6 +8901,16 @@
           <t>08935341301337</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>BATCH_00165</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
@@ -7251,6 +8951,16 @@
           <t>08935341301337</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>BATCH_00166</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
@@ -7291,6 +9001,16 @@
           <t>08935341301337</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>BATCH_00167</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
@@ -7331,6 +9051,16 @@
           <t>08935341301337</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>BATCH_00168</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
@@ -7371,6 +9101,16 @@
           <t>08935341301238</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>BATCH_00169</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr"/>
@@ -7411,6 +9151,16 @@
           <t>08935341301238</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>BATCH_00170</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
@@ -7451,6 +9201,16 @@
           <t>08935341301238</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>BATCH_00171</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
@@ -7491,6 +9251,16 @@
           <t>08935341301238</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>BATCH_00172</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
@@ -7531,6 +9301,16 @@
           <t>08935341301238</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>BATCH_00173</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr"/>
@@ -7571,6 +9351,16 @@
           <t>08935341300736</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>BATCH_00174</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
@@ -7611,6 +9401,16 @@
           <t>08935341300736</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>BATCH_00175</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr"/>
@@ -7651,6 +9451,16 @@
           <t>08935341300736</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>BATCH_00176</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr"/>
@@ -7691,6 +9501,16 @@
           <t>08935341300736</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>BATCH_00177</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr"/>
@@ -7731,6 +9551,16 @@
           <t>08935341300736</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>BATCH_00178</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr"/>
@@ -7771,6 +9601,16 @@
           <t>08935341300736</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>BATCH_00179</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr"/>
@@ -7811,6 +9651,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>BATCH_00180</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr"/>
@@ -7851,6 +9701,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>BATCH_00181</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr"/>
@@ -7891,6 +9751,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>BATCH_00182</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr"/>
@@ -7931,6 +9801,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>BATCH_00183</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr"/>
@@ -7971,6 +9851,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>BATCH_00184</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr"/>
@@ -8011,6 +9901,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>BATCH_00185</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr"/>
@@ -8051,6 +9951,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>BATCH_00186</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr"/>
@@ -8091,6 +10001,16 @@
           <t>8935341301832</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>BATCH_00187</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr"/>
@@ -8131,6 +10051,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>BATCH_00188</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr"/>
@@ -8171,6 +10101,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>BATCH_00189</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr"/>
@@ -8207,6 +10147,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>PENDING_00005</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr"/>
@@ -8247,6 +10197,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>BATCH_00190</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr"/>
@@ -8287,6 +10247,16 @@
           <t>18801062899613</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>BATCH_00191</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
@@ -8327,6 +10297,16 @@
           <t>18801062899613</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>BATCH_00192</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr"/>
@@ -8367,6 +10347,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>BATCH_00193</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr"/>
@@ -8407,6 +10397,16 @@
           <t>18801062899590</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>BATCH_00194</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr"/>
@@ -8443,6 +10443,16 @@
           <t>28801062475159</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PENDING_00006</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr"/>
@@ -8479,6 +10489,16 @@
           <t>18801062006202</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PENDING_00007</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr"/>
@@ -8515,6 +10535,16 @@
           <t>18801062000781</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PENDING_00008</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr"/>
@@ -8555,6 +10585,16 @@
           <t>18801062000781</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>BATCH_00195</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr"/>
@@ -8595,6 +10635,16 @@
           <t>58852008511258</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>BATCH_00196</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr"/>
@@ -8635,6 +10685,16 @@
           <t>58852008511258</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>BATCH_00197</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr"/>
@@ -8675,6 +10735,16 @@
           <t>58852008510053</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>BATCH_00198</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr"/>
@@ -8715,6 +10785,16 @@
           <t>8935341301832</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>BATCH_00199</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
@@ -8755,6 +10835,16 @@
           <t>14903333256812</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>BATCH_00200</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr"/>
@@ -8795,6 +10885,16 @@
           <t>38801062221975</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>BATCH_00201</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
@@ -8835,6 +10935,16 @@
           <t>38801062221197</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>BATCH_00202</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr"/>
@@ -8875,6 +10985,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>BATCH_00203</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr"/>
@@ -8915,6 +11035,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>BATCH_00204</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr"/>
@@ -8955,6 +11085,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>BATCH_00205</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr"/>
@@ -8995,6 +11135,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>BATCH_00206</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr"/>
@@ -9035,6 +11185,16 @@
           <t>38801062221975</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>BATCH_00207</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr"/>
@@ -9075,6 +11235,16 @@
           <t>58801062332255</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>BATCH_00208</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr"/>
@@ -9115,6 +11285,16 @@
           <t>38801062335610</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>BATCH_00209</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr"/>
@@ -9155,6 +11335,16 @@
           <t>38801062335610</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>BATCH_00210</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr"/>
@@ -9195,6 +11385,16 @@
           <t>38801062479925</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>BATCH_00211</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr"/>
@@ -9235,6 +11435,16 @@
           <t>68801062863756</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>BATCH_00212</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr"/>
@@ -9275,6 +11485,16 @@
           <t>68801062863756</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>BATCH_00213</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr"/>
@@ -9315,6 +11535,16 @@
           <t>68801062863756</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>BATCH_00214</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr"/>
@@ -9355,6 +11585,16 @@
           <t>14712834455118</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>BATCH_00215</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr"/>
@@ -9395,6 +11635,16 @@
           <t>14712834455118</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>BATCH_00216</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr"/>
@@ -9435,6 +11685,16 @@
           <t>04712834455166</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>BATCH_00217</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr"/>
@@ -9475,6 +11735,16 @@
           <t>04712834455166</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>BATCH_00218</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr"/>
@@ -9515,6 +11785,16 @@
           <t>14712834455187</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>BATCH_00219</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr"/>
@@ -9555,6 +11835,16 @@
           <t>04712834456378</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>BATCH_00220</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr"/>
@@ -9595,6 +11885,16 @@
           <t>04712834456378</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>BATCH_00221</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr"/>
@@ -9635,6 +11935,16 @@
           <t>04712834457153</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>BATCH_00222</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr"/>
@@ -9675,6 +11985,16 @@
           <t>08934677004912</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>BATCH_00223</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr"/>
@@ -9715,6 +12035,16 @@
           <t>08934677004936</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>BATCH_00224</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr"/>
@@ -9755,6 +12085,16 @@
           <t>08934677004929</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>BATCH_00225</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr"/>
@@ -9795,6 +12135,16 @@
           <t>14903333226129</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>BATCH_00226</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr"/>
@@ -9835,6 +12185,16 @@
           <t>14903333226129</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>BATCH_00227</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr"/>
@@ -9875,6 +12235,16 @@
           <t>14903333226129</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>BATCH_00228</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr"/>
@@ -9911,6 +12281,16 @@
           <t>14903333257451</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>PENDING_00009</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr"/>
@@ -9947,6 +12327,16 @@
           <t>14903333207142</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>PENDING_00010</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr"/>
@@ -9987,6 +12377,16 @@
           <t>14903333207142</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>BATCH_00229</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr"/>
@@ -10023,6 +12423,16 @@
           <t>48801062161889</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>PENDING_00011</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr"/>
@@ -10063,6 +12473,16 @@
           <t>18801062126221</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>BATCH_00230</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr"/>
@@ -10103,6 +12523,16 @@
           <t>18801062126184</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>BATCH_00231</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr"/>
@@ -10139,6 +12569,16 @@
           <t>18801062865687</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>PENDING_00012</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr"/>
@@ -10175,6 +12615,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>PENDING_00013</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr"/>
@@ -10215,6 +12665,16 @@
           <t>4712834456439</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>BATCH_00232</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr"/>
@@ -10255,6 +12715,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>BATCH_00233</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr"/>
@@ -10295,6 +12765,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>BATCH_00234</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr"/>
@@ -10335,6 +12815,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>BATCH_00235</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr"/>
@@ -10375,6 +12865,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>BATCH_00236</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr"/>
@@ -10415,6 +12915,16 @@
           <t>58852008300203</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>BATCH_00237</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr"/>
@@ -10455,6 +12965,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>BATCH_00238</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr"/>
@@ -10495,6 +13015,16 @@
           <t>58852008300234</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>BATCH_00239</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr"/>
@@ -10531,6 +13061,16 @@
           <t>58852008300784</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>PENDING_00014</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr"/>
@@ -10571,6 +13111,16 @@
           <t>58852008304867</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>BATCH_00240</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr"/>
@@ -10611,6 +13161,16 @@
           <t>58852008304898</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>BATCH_00241</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr"/>
@@ -10647,6 +13207,16 @@
           <t>58852008300265</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>PENDING_00015</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr"/>
@@ -10683,6 +13253,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>PENDING_00016</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr"/>
@@ -10723,6 +13303,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>BATCH_00242</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr"/>
@@ -10763,6 +13353,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>BATCH_00243</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr"/>
@@ -10803,6 +13403,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>BATCH_00244</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr"/>
@@ -10843,6 +13453,16 @@
           <t>58852008304911</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>BATCH_00245</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr"/>
@@ -10883,6 +13503,16 @@
           <t>58852008305413</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>BATCH_00246</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr"/>
@@ -10923,6 +13553,16 @@
           <t>58852008305673</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>BATCH_00247</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr"/>
@@ -10963,6 +13603,16 @@
           <t>58852008300265</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>BATCH_00248</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr"/>
@@ -11003,6 +13653,16 @@
           <t>58852008300296</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>BATCH_00249</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr"/>
@@ -11039,6 +13699,16 @@
           <t>58852008300982</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>PENDING_00017</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr"/>
@@ -11079,6 +13749,16 @@
           <t>58852008304911</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>BATCH_00250</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr"/>
@@ -11119,6 +13799,16 @@
           <t>58852008304935</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>BATCH_00251</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr"/>
@@ -11159,6 +13849,16 @@
           <t>58852008305390</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>BATCH_00252</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr"/>
@@ -11199,6 +13899,16 @@
           <t>58852008511258</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>BATCH_00253</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr"/>
@@ -11239,6 +13949,16 @@
           <t>58852008511258</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>BATCH_00254</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr"/>
@@ -11279,6 +13999,16 @@
           <t>58852008511258</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>BATCH_00255</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr"/>
@@ -11319,6 +14049,16 @@
           <t>58852008510053</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>BATCH_00256</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr"/>
@@ -11359,6 +14099,16 @@
           <t>58852008510510</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>BATCH_00257</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr"/>
@@ -11399,6 +14149,16 @@
           <t>58852008510510</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>BATCH_00258</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr"/>
@@ -11439,6 +14199,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>BATCH_00259</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr"/>
@@ -11479,6 +14249,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>BATCH_00260</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr"/>
@@ -11519,6 +14299,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>BATCH_00261</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr"/>
@@ -11559,6 +14349,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>BATCH_00262</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr"/>
@@ -11599,6 +14399,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>BATCH_00263</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr"/>
@@ -11639,6 +14449,16 @@
           <t>58852008306557</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>BATCH_00264</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr"/>
@@ -11679,6 +14499,16 @@
           <t>58852008306595</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>BATCH_00265</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr"/>
@@ -11719,6 +14549,16 @@
           <t>08935341301238</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>BATCH_00266</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr"/>
@@ -11755,6 +14595,16 @@
           <t>08935341300637</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>PENDING_00018</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr"/>
@@ -11791,6 +14641,16 @@
           <t>18801062633460</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>PENDING_00019</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr"/>
@@ -11831,6 +14691,16 @@
           <t>18801062633460</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>BATCH_00267</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr"/>
@@ -11871,6 +14741,16 @@
           <t>18801062633460</t>
         </is>
       </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>BATCH_00268</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr"/>
@@ -11907,6 +14787,16 @@
           <t>14903333270665</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>PENDING_00020</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr"/>
@@ -11943,6 +14833,16 @@
           <t>34903333219835</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>PENDING_00021</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr"/>
@@ -11983,6 +14883,16 @@
           <t>14903333256812</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>BATCH_00269</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr"/>
@@ -12019,6 +14929,16 @@
           <t>68801062332115</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>PENDING_00022</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr"/>
@@ -12059,6 +14979,16 @@
           <t>68801062332115</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>BATCH_00270</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr"/>
@@ -12099,6 +15029,16 @@
           <t>68801062332115</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>BATCH_00271</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr"/>
@@ -12139,6 +15079,16 @@
           <t>38801062221975</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>BATCH_00272</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr"/>
@@ -12179,6 +15129,16 @@
           <t>38801062221975</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>BATCH_00273</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr"/>
@@ -12219,6 +15179,16 @@
           <t>38801062221975</t>
         </is>
       </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>BATCH_00274</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr"/>
@@ -12259,6 +15229,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>BATCH_00275</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr"/>
@@ -12299,6 +15279,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>BATCH_00276</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr"/>
@@ -12339,6 +15329,16 @@
           <t>38801062221197</t>
         </is>
       </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>BATCH_00277</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr"/>
@@ -12379,6 +15379,16 @@
           <t>38801062221197</t>
         </is>
       </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>BATCH_00278</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr"/>
@@ -12415,6 +15425,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>PENDING_00023</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr"/>
@@ -12451,6 +15471,16 @@
           <t>58801062009522</t>
         </is>
       </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>PENDING_00024</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr"/>
@@ -12491,6 +15521,16 @@
           <t>68801062863756</t>
         </is>
       </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>BATCH_00279</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr"/>
@@ -12531,6 +15571,16 @@
           <t>68801062863756</t>
         </is>
       </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>BATCH_00280</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr"/>
@@ -12571,6 +15621,16 @@
           <t>68801062863756</t>
         </is>
       </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>BATCH_00281</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr"/>
@@ -12607,6 +15667,16 @@
           <t>04712834457320</t>
         </is>
       </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>PENDING_00025</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr"/>
@@ -12643,6 +15713,16 @@
           <t>4712834457344</t>
         </is>
       </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>PENDING_00026</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr"/>
@@ -12683,6 +15763,16 @@
           <t>04712834457429</t>
         </is>
       </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>BATCH_00282</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr"/>
@@ -12711,6 +15801,16 @@
       </c>
       <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>PENDING_00027</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr"/>
@@ -12747,6 +15847,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr"/>
@@ -12783,6 +15893,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr"/>
@@ -12819,6 +15939,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr"/>
@@ -12855,6 +15985,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr"/>
@@ -12891,6 +16031,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr"/>
@@ -12927,6 +16077,16 @@
           <t>18801062865717</t>
         </is>
       </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr"/>
@@ -12963,6 +16123,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr"/>
@@ -12999,6 +16169,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr"/>
@@ -13035,6 +16215,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr"/>
@@ -13071,6 +16261,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr"/>
@@ -13107,6 +16307,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr"/>
@@ -13143,6 +16353,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr"/>
@@ -13179,6 +16399,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr"/>
@@ -13215,6 +16445,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr"/>
@@ -13251,6 +16491,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr"/>
@@ -13287,6 +16537,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr"/>
@@ -13323,6 +16583,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr"/>
@@ -13359,6 +16629,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr"/>
@@ -13395,6 +16675,16 @@
           <t>28801062639483</t>
         </is>
       </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr"/>
@@ -13431,6 +16721,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr"/>
@@ -13467,6 +16767,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr"/>
@@ -13503,6 +16813,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr"/>
@@ -13539,6 +16859,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr"/>
@@ -13575,6 +16905,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr"/>
@@ -13611,6 +16951,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr"/>
@@ -13647,6 +16997,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr"/>
@@ -13683,6 +17043,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr"/>
@@ -13719,6 +17089,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr"/>
@@ -13755,6 +17135,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr"/>
@@ -13791,6 +17181,16 @@
           <t>18801062132765</t>
         </is>
       </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr"/>
@@ -13827,6 +17227,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr"/>
@@ -13863,6 +17273,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr"/>
@@ -13899,6 +17319,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr"/>
@@ -13935,6 +17365,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr"/>
@@ -13971,6 +17411,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr"/>
@@ -14007,6 +17457,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr"/>
@@ -14043,6 +17503,16 @@
           <t>78801062267711</t>
         </is>
       </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr"/>
@@ -14079,6 +17549,16 @@
           <t>78801062267711</t>
         </is>
       </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr"/>
@@ -14115,6 +17595,16 @@
           <t>78801062267711</t>
         </is>
       </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr"/>
@@ -14151,6 +17641,16 @@
           <t>78801062267711</t>
         </is>
       </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr"/>
@@ -14187,6 +17687,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr"/>
@@ -14223,6 +17733,16 @@
           <t>28801062481730</t>
         </is>
       </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr"/>
@@ -14259,6 +17779,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr"/>
@@ -14295,6 +17825,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr"/>
@@ -14331,6 +17871,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr"/>
@@ -14367,6 +17917,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr"/>
@@ -14403,6 +17963,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr"/>
@@ -14439,6 +18009,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr"/>
@@ -14475,6 +18055,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr"/>
@@ -14511,6 +18101,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr"/>
@@ -14547,6 +18147,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr"/>
@@ -14583,6 +18193,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr"/>
@@ -14619,6 +18239,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr"/>
@@ -14655,6 +18285,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr"/>
@@ -14691,6 +18331,16 @@
           <t>28801062639483</t>
         </is>
       </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr"/>
@@ -14727,6 +18377,16 @@
           <t>28801062639483</t>
         </is>
       </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr"/>
@@ -14763,6 +18423,16 @@
           <t>28801062639483</t>
         </is>
       </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr"/>
@@ -14799,6 +18469,16 @@
           <t>18801062881748</t>
         </is>
       </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr"/>
@@ -14835,6 +18515,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr"/>
@@ -14871,6 +18561,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr"/>
@@ -14907,6 +18607,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr"/>
@@ -14943,6 +18653,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr"/>
@@ -14979,6 +18699,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr"/>
@@ -15015,6 +18745,16 @@
           <t>18801062132765</t>
         </is>
       </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr"/>
@@ -15051,6 +18791,16 @@
           <t>18801062132765</t>
         </is>
       </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr"/>
@@ -15087,6 +18837,16 @@
           <t>18801062132765</t>
         </is>
       </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr"/>
@@ -15123,6 +18883,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr"/>
@@ -15159,6 +18929,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr"/>
@@ -15195,6 +18975,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr"/>
@@ -15231,6 +19021,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr"/>
@@ -15267,6 +19067,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr"/>
@@ -15303,6 +19113,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr"/>
@@ -15339,6 +19159,16 @@
           <t>18801062126481</t>
         </is>
       </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr"/>
@@ -15375,6 +19205,16 @@
           <t>18801062126481</t>
         </is>
       </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr"/>
@@ -15411,6 +19251,16 @@
           <t>18801062126481</t>
         </is>
       </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr"/>
@@ -15447,6 +19297,16 @@
           <t>18801062126481</t>
         </is>
       </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr"/>
@@ -15483,6 +19343,16 @@
           <t>28801062639483</t>
         </is>
       </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr"/>
@@ -15519,6 +19389,16 @@
           <t>28801062639483</t>
         </is>
       </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr"/>
@@ -15555,6 +19435,16 @@
           <t>78801062267711</t>
         </is>
       </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr"/>
@@ -15591,6 +19481,16 @@
           <t>78801062267711</t>
         </is>
       </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr"/>
@@ -15627,6 +19527,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr"/>
@@ -15663,6 +19573,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr"/>
@@ -15699,6 +19619,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr"/>
@@ -15735,6 +19665,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr"/>
@@ -15771,6 +19711,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr"/>
@@ -15807,6 +19757,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr"/>
@@ -15843,6 +19803,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr"/>
@@ -15879,6 +19849,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr"/>
@@ -15915,6 +19895,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr"/>
@@ -15951,6 +19941,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr"/>
@@ -15987,6 +19987,16 @@
           <t>28801062481730</t>
         </is>
       </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr"/>
@@ -16023,6 +20033,16 @@
           <t>48801062016097</t>
         </is>
       </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr"/>
@@ -16059,6 +20079,16 @@
           <t>48801062016097</t>
         </is>
       </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr"/>
@@ -16095,6 +20125,16 @@
           <t>48801062016097</t>
         </is>
       </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr"/>
@@ -16131,6 +20171,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr"/>
@@ -16167,6 +20217,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr"/>
@@ -16203,6 +20263,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr"/>
@@ -16239,6 +20309,16 @@
           <t>18801062881748</t>
         </is>
       </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr"/>
@@ -16275,6 +20355,16 @@
           <t>18801062880147</t>
         </is>
       </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr"/>
@@ -16311,6 +20401,16 @@
           <t>18801062880147</t>
         </is>
       </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr"/>
@@ -16347,6 +20447,16 @@
           <t>48801062016097</t>
         </is>
       </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr"/>
@@ -16383,6 +20493,16 @@
           <t>48801062016097</t>
         </is>
       </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr"/>
@@ -16419,6 +20539,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr"/>
@@ -16455,6 +20585,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr"/>
@@ -16491,6 +20631,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr"/>
@@ -16527,6 +20677,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr"/>
@@ -16563,6 +20723,16 @@
           <t>48801062267796</t>
         </is>
       </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr"/>
@@ -16599,6 +20769,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr"/>
@@ -16635,6 +20815,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr"/>
@@ -16671,6 +20861,16 @@
           <t>48801062641237</t>
         </is>
       </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr"/>
@@ -16707,6 +20907,16 @@
           <t>18801062880888</t>
         </is>
       </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr"/>
@@ -16743,6 +20953,16 @@
           <t>18801062865717</t>
         </is>
       </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr"/>
@@ -16779,6 +20999,16 @@
           <t>18801062132765</t>
         </is>
       </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr"/>
@@ -16815,6 +21045,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr"/>
@@ -16851,6 +21091,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr"/>
@@ -16887,6 +21137,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr"/>
@@ -16923,6 +21183,16 @@
           <t>98801062478166</t>
         </is>
       </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr"/>
@@ -16959,6 +21229,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr"/>
@@ -16995,6 +21275,16 @@
           <t>58801062636353</t>
         </is>
       </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr"/>
@@ -17031,6 +21321,16 @@
           <t>18801062126481</t>
         </is>
       </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr"/>
@@ -17067,6 +21367,16 @@
           <t>28801062481730</t>
         </is>
       </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr"/>
@@ -17103,6 +21413,16 @@
           <t>28801062481730</t>
         </is>
       </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr"/>
@@ -17139,6 +21459,16 @@
           <t>18801062881748</t>
         </is>
       </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr"/>
@@ -17175,6 +21505,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr"/>
@@ -17211,6 +21551,16 @@
           <t>18801062862532</t>
         </is>
       </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr"/>
@@ -17247,6 +21597,16 @@
           <t>28801062481730</t>
         </is>
       </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr"/>
@@ -17283,6 +21643,16 @@
           <t>18801062860521</t>
         </is>
       </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr"/>
@@ -17319,6 +21689,16 @@
           <t>18801062860521</t>
         </is>
       </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr"/>
@@ -17355,6 +21735,16 @@
           <t>18801062016096</t>
         </is>
       </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr"/>
@@ -17391,6 +21781,16 @@
           <t>28801062482201</t>
         </is>
       </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr"/>
@@ -17427,6 +21827,16 @@
           <t>68801062479834</t>
         </is>
       </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr"/>
@@ -17463,6 +21873,16 @@
           <t>14903333258847</t>
         </is>
       </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr"/>
@@ -17499,6 +21919,16 @@
           <t>14903333220448</t>
         </is>
       </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr"/>
@@ -17535,6 +21965,16 @@
           <t>44903333248733</t>
         </is>
       </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr"/>
@@ -17569,6 +22009,16 @@
       <c r="J445" t="inlineStr">
         <is>
           <t>44903333207235</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>AIRCON</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:36:49</t>
         </is>
       </c>
     </row>
